--- a/data/ayurvedic_medicines.xlsx
+++ b/data/ayurvedic_medicines.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2048,6 +2048,38 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Varicose-vein-type condition</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sahacharadi Thailam, Kaishore Guggulu, Sarivadyasava</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sahacharadi Thailam: gentle upward external massage; Kaishore Guggulu: 2 tabs twice daily; Sarivadyasava: 20ml post meals</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2-3 months</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>High-fiber diet, citrus fruits, berries, avoid excessive salty and constipating foods</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Leg elevation when resting, avoid prolonged standing, gentle walking</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
